--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C197"/>
+  <dimension ref="A1:C198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3764,6 +3764,23 @@
         </is>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>10月13日</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>张水龙</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>打样：鱼一斤三左右（约1.3斤/尾），长势好（9月28日打样为七两左右）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C198"/>
+  <dimension ref="A1:C199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3781,6 +3781,23 @@
         </is>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>10月13日</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>丁杰秋</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>测水客情服务（通威用户回访）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C199"/>
+  <dimension ref="A1:C202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3798,6 +3798,57 @@
         </is>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>10月13日</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>丁力强</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>基地客勤+测水10口塘：3号塘(西坡村)7.0/0.2/0.10；5号塘7.4/0.2/0.05、4号塘7.2/0.2/0.05、2号塘7.4/0.2/0.10、1号塘8.6/0.2/0.05（均西坡村）；6号塘7.2/0.40/0.10、10号塘7.4/0.20/0.10（信坡村）；7号塘7.2/0.90/0.05、8号塘7.4/0.90/0.10、9号塘7.2/0.90/0.10（南排坡），三项均正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>10月13日</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>丁伟峰</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>客勤+测水1/2/4/3号塘（罗豆农场猪场）：7.4/0.5/0.05、7.2/0.9/0.10、7.2/0.9/0.10、7.2/0.2/0.10，三项均正常；另有4口塘已出鱼（合计约8口），与丁茂溪同用海一</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>10月13日</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>梁修成</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>走访（新名建档）：现用海大2552，仓存充足（刚到一批），转化宜缓；约10.14早测水</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -3811,7 +3811,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>基地客勤+测水10口塘：3号塘(西坡村)7.0/0.2/0.10；5号塘7.4/0.2/0.05、4号塘7.2/0.2/0.05、2号塘7.4/0.2/0.10、1号塘8.6/0.2/0.05（均西坡村）；6号塘7.2/0.40/0.10、10号塘7.4/0.20/0.10（信坡村）；7号塘7.2/0.90/0.05、8号塘7.4/0.90/0.10、9号塘7.2/0.90/0.10（南排坡），三项均正常</t>
+          <t>基地客勤+测水10口塘：3号塘(西坡村)7.0/0.2/0.10；5号塘7.4/0.2/0.005、4号塘7.2/0.2/0.005、2号塘7.4/0.2/0.10、1号塘8.6/0.2/0.005（均西坡村）；6号塘7.2/0.40/0.10、10号塘7.4/0.20/0.10（信坡村）；7号塘7.2/0.90/0.05、8号塘7.4/0.90/0.10、9号塘7.2/0.90/0.10（南排坡），三项均正常</t>
         </is>
       </c>
     </row>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C202"/>
+  <dimension ref="A1:C214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3849,6 +3849,194 @@
         </is>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>10月14日</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>樊法云</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>拜访交谈用料情况：现用海一、海大，之前拉过通威、打样效果不好也没全程用，对换料接受度低；待其下一批拿料节点再探通威转化窗口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>10月14日</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>梁修成</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>拜访交谈用料情况：同樊法云，用到一半打样效果不好即停；混料差异难看出谁家饲料更好或者更次，打样不彻底则对比无据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>10月14日</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>王焕忠</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>拜访交谈用料情况：同樊法云，用到一半打样效果不好即停。</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>10月14日</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>丁力强</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>协助马总放石斑进塘。</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>10月14日</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>潘如府</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>反映黑黄料问题，料塔迟迟未动工；黑黄料涉及饲料品牌与批次待取样核实，料塔未动工原因与预计工期待跟进。</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>10月15日</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>吴焕亮</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>客情走访。</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>10月15日</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>云维军</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>客情走访：基地与冯学新基地合并（用户口述「冯学兴」，同音变体）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>10月15日</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>郑国庆</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>客情走访。</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>10月15日</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>丁旭华</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>客情走访：存塘约20万苗，计划2027年4月抓鱼；这一造鱼大的7两左右、小的6两左右。</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>10月15日</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>梁修成</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>走访中获悉：存塘罗非50万苗。</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>10月15日</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>樊法云</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>走访中获悉：存塘罗非30万苗（用户本次记作「樊法元」，同音变体）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="214"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C214"/>
+  <dimension ref="A1:C217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4036,7 +4036,74 @@
         </is>
       </c>
     </row>
-    <row r="214"/>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>10月16日</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>丁杰秋</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>大致坡基地第三轮打样：1号1.02、2号0.81、3号0.77、4号0.53、5号0.54、6号0.99、7号0.83斤/条，较9月29日涨0.17-0.31，1号过斤；交谈后续用料计划；查阅8-10月投料台账，用量持续攀升，10月日均约76包</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>10月16日</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>张水龙</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>走访，今日未打样；约定10月23日再来打样测水（底下那口塘）</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>10月16日</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>榆林舰</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>走访（新接触）</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>10月16日</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>朱耀武</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>走访未遇本人：去接小孩，改日再访</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C217"/>
+  <dimension ref="A1:C225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4104,6 +4104,142 @@
         </is>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>10月17日</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>施君华</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>沟通转料：现用天祥料价格113，与我司产品价格层级不符，转料非常困难，后续继续跟进</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>10月19日</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>丁杰秋</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>大致坡基地打样，解答该基地鱼长势偏慢的疑问；4号塘计划本月底出鱼，后续跟进出鱼安排与用料情况</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>10月19日</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>陈老板</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>走访（新接触）：养殖叉尾，维护客情，基本情况待跟进</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>10月22日</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>王卫明</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>拜访（新接触）：现用海大2552，跟王焕忠拿料；存塘鱼八两左右，之前用百洋料，这一造全程用海大，说明年用料再考虑通威</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>10月22日</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>徐在苏</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>走访：老板休息；明天抓最后一车鱼，明天再访</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>10月23日</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>张水龙</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>打样测水：1号苗塘10月21日放苗14万尾、亚盐偏高0.3左右踩报警线；2号条均八两存塘7万尾；3号条均预计1.4斤以上（10月13日1.35斤）；2号3号水质正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>10月23日</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>徐在苏</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>抓鱼回访：一号塘包产35因死鱼严重、二号塘包产38、三号塘未抓完；老徐自述包产不过40系鱼苗问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>10月23日</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>丁力强</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>积炭素累计用到100包，今天拉了33包</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C225"/>
+  <dimension ref="A1:C232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4240,6 +4240,125 @@
         </is>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>10月24日</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>丁志开</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>测水+打样：3号塘pH8.0（鱼苗塘，已拿苗50万尾）；6号塘氨氮、亚盐双高⚠️，需2天内复测取具体数值并给调水建议；打样2号塘八两、4号塘一斤、5号塘一斤、6号塘8两。</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>10月24日</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>丁旭华</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>用户要求打样，查看酵益宝的养殖情况。</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>10月24日</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>陈吉</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>今天抓鱼，前往看情况，出鱼中，出完再联系。</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>10月25日</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>丁旭华</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>对接打样，案例佐证酵益宝效果。</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>10月25日</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>云维军</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>拿料受限于冯学新。</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>10月25日</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>施锦云</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>用户不在，择日再访。</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>10月25日</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>丁力强</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>送冻宝和药物，客情维护。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -729,7 +729,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>陈守健</t>
+          <t>陈守建</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>丁志杰</t>
+          <t>丁志开</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>丁立强</t>
+          <t>丁力强</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>施军华</t>
+          <t>施君华</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>丁立强</t>
+          <t>丁力强</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>丁立强</t>
+          <t>丁力强</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>丁立强</t>
+          <t>丁力强</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>司君华</t>
+          <t>施君华</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>丁立强</t>
+          <t>丁力强</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -4333,7 +4333,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>施锦云</t>
+          <t>施景云</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>送冻宝和药物，客情维护。</t>
+          <t>送动保和药物，客情维护。</t>
         </is>
       </c>
     </row>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C232"/>
+  <dimension ref="A1:C234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4359,6 +4359,40 @@
         </is>
       </c>
     </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>10月27日</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>张水龙</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>客情走访+测水：1号苗塘经硝硝乐（消消乐同音）处理，原亚盐0.3+踩线已降至正常；2号塘亚盐0.25临界接近0.3警戒线、预计约20天出鱼；用户想培育光合菌；3号塘未测。</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>10月27日</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>徐在苏</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>出鱼回访：最后一口塘未干塘、已抓8万多、包产约39；用户反馈鱼苗质量太低，与10.23老徐自述包产不过40系鱼苗问题相互印证；用料品牌仍待补。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C234"/>
+  <dimension ref="A1:C235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4393,6 +4393,23 @@
         </is>
       </c>
     </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>10月27日</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>丁力强</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>测水：西坡村1/2/3/4/5号塘，pH、氨氮、亚盐均正常，无异常。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -4372,7 +4372,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>客情走访+测水：1号苗塘经硝硝乐（消消乐同音）处理，原亚盐0.3+踩线已降至正常；2号塘亚盐0.25临界接近0.3警戒线、预计约20天出鱼；用户想培育光合菌；3号塘未测。</t>
+          <t>客情走访+测水（比色卡目视实测，铺前镇华兰村）：1号苗塘pH7.1/氨氮0.20/亚盐0.15（硝硝乐处理后正常）、2号塘pH6.9/氨氮0/亚盐0.20（临界临近0.3警戒线，预计约20天出鱼）、3号塘pH7.2/氨氮0/亚盐0.05（原未测补测）；用户想培育光合菌。</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>测水：西坡村1/2/3/4/5号塘，pH、氨氮、亚盐均正常，无异常。</t>
+          <t>测水（比色卡目视实测）：1号塘(罗豆农场猪场)pH7.2/氨氮0.20/亚盐0、2号塘(西坡村)pH7.4/氨氮0.60/亚盐0.10(五口最高，回访重点)、3号塘pH7.2/氨氮0.60/亚盐0.005、4号塘pH7.0/氨氮0.20/亚盐0、5号塘pH7.2/氨氮0.20/亚盐0.01；全部在安全线内。</t>
         </is>
       </c>
     </row>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C235"/>
+  <dimension ref="A1:C239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4410,6 +4410,74 @@
         </is>
       </c>
     </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>10月7日</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>陶伟静</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>客情走访。现用海大2552料，跟吴建龙拿料，产量不太高，比较反感业务员问这问那，从其用料和养殖情况看有转化机会。</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>10月7日</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>张秋海</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>客情走访，用户不在场。见塘口有无人机作业，其塘三口，推断无人机非自购，应该是海大动保飞防服务，用料情况待下次走访核实。</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>10月7日</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>吴杨松</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>客情走访。现用歌颂饲料，跟冯学新拿现金料105元/包（正常价121元）；早年用过通威沉水颗粒料，后用过百洋（反馈一般），现转歌颂，元旦前抓鱼。</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>10月7日</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>韩利光</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>客情走访。跟昌盛（其同学）拿料，现混用金长城+百洋+海大；塘口正在修投料机，此前停养一段时间，现打算恢复养殖，有问到过通威包产如何，推荐我司饲料。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C239"/>
+  <dimension ref="A1:C240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4478,6 +4478,23 @@
         </is>
       </c>
     </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>陈老板（#122·10.19新接触）</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>今日走访补全基本情况：鱼塘约2.3亩（养鱼）；另有1口虾苗塘（苗塘），用宝路苗</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -4486,12 +4486,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>陈老板（#122·10.19新接触）</t>
+          <t>王老板</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>今日走访补全基本情况：鱼塘约2.3亩（养鱼）；另有1口虾苗塘（苗塘），用宝路苗</t>
+          <t>今日走访：鱼塘约2.3亩（养鱼）；另有1口虾苗塘（苗塘），用宝路苗（两个塘在养）</t>
         </is>
       </c>
     </row>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C240"/>
+  <dimension ref="A1:C241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4495,6 +4495,23 @@
         </is>
       </c>
     </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>陈老板（#122·养殖叉尾）</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>今日走访：养殖叉尾，现用天翔2号料</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
